--- a/instance_records_PMSP_V0.1.xlsx
+++ b/instance_records_PMSP_V0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mazyk\OneDrive\Desktop\Thesis\Metaheuristics\Publication\git-hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54853968-080A-4300-BA9F-A94DCA73F2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673A344A-C59C-4457-8447-99BF25741E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
   <si>
     <t>Instance Details</t>
   </si>
@@ -1284,6 +1284,222 @@
   </si>
   <si>
     <t>J360_M10_P9_W1_TW1.0_ME1.0_AP0.txt</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_172.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_173.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_174.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_175.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_176.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_177.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_178.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_179.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_180.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_181.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_182.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_183.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_184.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_185.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_186.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_187.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_188.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_189.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_190.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_191.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_192.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_193.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_194.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_195.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_196.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_197.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_198.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_199.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_200.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_201.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_202.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_203.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_204.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_205.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_206.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_207.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_208.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_209.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_210.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_211.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_212.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_213.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_214.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_215.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_216.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_217.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_218.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_219.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_220.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_221.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_222.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_223.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_224.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_225.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_226.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_227.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_228.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_229.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_230.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_231.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_232.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_233.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_234.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_235.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_236.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_237.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_238.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_239.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_240.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_241.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_242.xlsx</t>
+  </si>
+  <si>
+    <t>Scheduling_Instance_243.xlsx</t>
   </si>
 </sst>
 </file>
@@ -3046,7 +3262,7 @@
         <v>344</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>2</v>
+        <v>416</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -3054,7 +3270,7 @@
         <v>345</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>3</v>
+        <v>417</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -3062,7 +3278,7 @@
         <v>346</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>4</v>
+        <v>418</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -3070,7 +3286,7 @@
         <v>347</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>5</v>
+        <v>419</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -3078,7 +3294,7 @@
         <v>348</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>6</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -3086,7 +3302,7 @@
         <v>349</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>7</v>
+        <v>421</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -3094,7 +3310,7 @@
         <v>350</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>8</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -3102,7 +3318,7 @@
         <v>351</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>9</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -3110,7 +3326,7 @@
         <v>352</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>10</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -3118,7 +3334,7 @@
         <v>353</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>11</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -3126,7 +3342,7 @@
         <v>354</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>12</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -3134,7 +3350,7 @@
         <v>355</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>13</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -3142,7 +3358,7 @@
         <v>356</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>14</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -3150,7 +3366,7 @@
         <v>357</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>15</v>
+        <v>429</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -3158,7 +3374,7 @@
         <v>358</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>16</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -3166,7 +3382,7 @@
         <v>359</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>17</v>
+        <v>431</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -3174,7 +3390,7 @@
         <v>360</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>18</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -3182,7 +3398,7 @@
         <v>361</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>19</v>
+        <v>433</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -3190,7 +3406,7 @@
         <v>362</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>20</v>
+        <v>434</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -3198,7 +3414,7 @@
         <v>363</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>21</v>
+        <v>435</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -3206,7 +3422,7 @@
         <v>364</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>22</v>
+        <v>436</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -3214,7 +3430,7 @@
         <v>365</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>23</v>
+        <v>437</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -3222,7 +3438,7 @@
         <v>366</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>24</v>
+        <v>438</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -3230,7 +3446,7 @@
         <v>367</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>25</v>
+        <v>439</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -3238,7 +3454,7 @@
         <v>368</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>26</v>
+        <v>440</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -3246,7 +3462,7 @@
         <v>369</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>27</v>
+        <v>441</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -3254,7 +3470,7 @@
         <v>370</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>28</v>
+        <v>442</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -3262,7 +3478,7 @@
         <v>371</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>29</v>
+        <v>443</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -3270,7 +3486,7 @@
         <v>372</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>30</v>
+        <v>444</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -3278,7 +3494,7 @@
         <v>373</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>31</v>
+        <v>445</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -3286,7 +3502,7 @@
         <v>374</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>32</v>
+        <v>446</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -3294,7 +3510,7 @@
         <v>375</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>33</v>
+        <v>447</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -3302,7 +3518,7 @@
         <v>376</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>34</v>
+        <v>448</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -3310,7 +3526,7 @@
         <v>377</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>35</v>
+        <v>449</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -3318,7 +3534,7 @@
         <v>378</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>36</v>
+        <v>450</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -3326,7 +3542,7 @@
         <v>379</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>37</v>
+        <v>451</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -3334,7 +3550,7 @@
         <v>380</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>38</v>
+        <v>452</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -3342,7 +3558,7 @@
         <v>381</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>39</v>
+        <v>453</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -3350,7 +3566,7 @@
         <v>382</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>40</v>
+        <v>454</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -3358,7 +3574,7 @@
         <v>383</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>41</v>
+        <v>455</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -3366,7 +3582,7 @@
         <v>384</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>42</v>
+        <v>456</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -3374,7 +3590,7 @@
         <v>385</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>43</v>
+        <v>457</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -3382,7 +3598,7 @@
         <v>386</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>44</v>
+        <v>458</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -3390,7 +3606,7 @@
         <v>387</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>45</v>
+        <v>459</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -3398,7 +3614,7 @@
         <v>388</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>46</v>
+        <v>460</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -3406,7 +3622,7 @@
         <v>389</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>47</v>
+        <v>461</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -3414,7 +3630,7 @@
         <v>390</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>48</v>
+        <v>462</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -3422,7 +3638,7 @@
         <v>391</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>49</v>
+        <v>463</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -3430,7 +3646,7 @@
         <v>392</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>50</v>
+        <v>464</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -3438,7 +3654,7 @@
         <v>393</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>51</v>
+        <v>465</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -3446,7 +3662,7 @@
         <v>394</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>52</v>
+        <v>466</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
@@ -3454,7 +3670,7 @@
         <v>395</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>53</v>
+        <v>467</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -3462,7 +3678,7 @@
         <v>396</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>54</v>
+        <v>468</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
@@ -3470,7 +3686,7 @@
         <v>397</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>55</v>
+        <v>469</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -3478,7 +3694,7 @@
         <v>398</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>56</v>
+        <v>470</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
@@ -3486,7 +3702,7 @@
         <v>399</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>57</v>
+        <v>471</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
@@ -3494,7 +3710,7 @@
         <v>400</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>58</v>
+        <v>472</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
@@ -3502,7 +3718,7 @@
         <v>401</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>59</v>
+        <v>473</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
@@ -3510,7 +3726,7 @@
         <v>402</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>60</v>
+        <v>474</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
@@ -3518,7 +3734,7 @@
         <v>403</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>61</v>
+        <v>475</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
@@ -3526,7 +3742,7 @@
         <v>404</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>62</v>
+        <v>476</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
@@ -3534,7 +3750,7 @@
         <v>405</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>63</v>
+        <v>477</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
@@ -3542,7 +3758,7 @@
         <v>406</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>64</v>
+        <v>478</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
@@ -3550,7 +3766,7 @@
         <v>407</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>65</v>
+        <v>479</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
@@ -3558,7 +3774,7 @@
         <v>408</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>66</v>
+        <v>480</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
@@ -3566,7 +3782,7 @@
         <v>409</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>67</v>
+        <v>481</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
@@ -3574,7 +3790,7 @@
         <v>410</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>68</v>
+        <v>482</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
@@ -3582,7 +3798,7 @@
         <v>411</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>69</v>
+        <v>483</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -3590,7 +3806,7 @@
         <v>412</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>70</v>
+        <v>484</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -3598,7 +3814,7 @@
         <v>413</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>71</v>
+        <v>485</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
@@ -3606,7 +3822,7 @@
         <v>414</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>72</v>
+        <v>486</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
@@ -3614,7 +3830,7 @@
         <v>415</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>73</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
